--- a/assets/docs/lop5/Tin hoc - Lop 5.xlsx
+++ b/assets/docs/lop5/Tin hoc - Lop 5.xlsx
@@ -1390,7 +1390,8 @@
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.2 CB2b: HS tự kiểm thử đủ các trường hợp và sửa được trường hợp chương trình xử lí sai.</t>
+          <t>Năng lực số 5.2 CB2b: HS tự kiểm thử đủ các trường hợp và sửa được trường hợp chương trình xử lí sai.
+STEM: Trò chơi điều khiển robot tránh chướng ngại vật (Tin học – Toán – Công nghệ) — dạy thay cho tiết này.</t>
         </is>
       </c>
     </row>
